--- a/turni_medici.xlsx
+++ b/turni_medici.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mdigital-my.sharepoint.com/personal/x238574_one_merckgroup_com/Documents/Desktop/PERSONALI/PEGASO/ELABORATO TESI/Rev.9.0 -- CLEAR_OPTIMIZE_CODE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mdigital-my.sharepoint.com/personal/x238574_one_merckgroup_com/Documents/Desktop/PERSONALI/PEGASO/ELABORATO TESI/Release 8.0 -- CLEAR_OPTIMIZE_CODE/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="11_F25DC773A252ABDACC1048E6D1DB51785BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D844984-521D-4463-B994-CEB3920DC182}"/>
+  <xr:revisionPtr revIDLastSave="151" documentId="11_F25DC773A252ABDACC1048E6D1DB51785BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD4AC267-9E83-40FB-85B4-1FFE98DE009A}"/>
   <bookViews>
-    <workbookView xWindow="-13296" yWindow="-16380" windowWidth="29016" windowHeight="15696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15504" yWindow="-16308" windowWidth="29016" windowHeight="15696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SPECIALIZZAZIONI" sheetId="1" r:id="rId1"/>
@@ -775,7 +775,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="5">
-        <v>46183</v>
+        <v>46305</v>
       </c>
       <c r="C2" s="6">
         <v>0.33333333333333331</v>
@@ -789,7 +789,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5">
-        <v>46184</v>
+        <v>46306</v>
       </c>
       <c r="C3" s="6">
         <v>0.33333333333333331</v>
@@ -803,7 +803,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="5">
-        <v>46185</v>
+        <v>46307</v>
       </c>
       <c r="C4" s="6">
         <v>0.33333333333333331</v>
@@ -817,7 +817,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="5">
-        <v>46186</v>
+        <v>46308</v>
       </c>
       <c r="C5" s="6">
         <v>0.33333333333333331</v>
@@ -831,7 +831,7 @@
         <v>29</v>
       </c>
       <c r="B6" s="5">
-        <v>46187</v>
+        <v>46309</v>
       </c>
       <c r="C6" s="6">
         <v>0.33333333333333331</v>
@@ -845,7 +845,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="5">
-        <v>46188</v>
+        <v>46310</v>
       </c>
       <c r="C7" s="6">
         <v>0.33333333333333331</v>
@@ -859,7 +859,7 @@
         <v>34</v>
       </c>
       <c r="B8" s="5">
-        <v>46189</v>
+        <v>46311</v>
       </c>
       <c r="C8" s="6">
         <v>0.33333333333333331</v>
@@ -873,7 +873,7 @@
         <v>35</v>
       </c>
       <c r="B9" s="5">
-        <v>46190</v>
+        <v>46312</v>
       </c>
       <c r="C9" s="6">
         <v>0.33333333333333331</v>
@@ -887,7 +887,7 @@
         <v>36</v>
       </c>
       <c r="B10" s="5">
-        <v>46191</v>
+        <v>46313</v>
       </c>
       <c r="C10" s="6">
         <v>0.33333333333333331</v>
@@ -901,7 +901,7 @@
         <v>37</v>
       </c>
       <c r="B11" s="5">
-        <v>46192</v>
+        <v>46314</v>
       </c>
       <c r="C11" s="6">
         <v>0.33333333333333331</v>
@@ -915,7 +915,7 @@
         <v>38</v>
       </c>
       <c r="B12" s="5">
-        <v>46193</v>
+        <v>46315</v>
       </c>
       <c r="C12" s="6">
         <v>0.33333333333333331</v>
@@ -929,7 +929,7 @@
         <v>39</v>
       </c>
       <c r="B13" s="5">
-        <v>46194</v>
+        <v>46316</v>
       </c>
       <c r="C13" s="6">
         <v>0.33333333333333331</v>
@@ -943,7 +943,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="5">
-        <v>46195</v>
+        <v>46317</v>
       </c>
       <c r="C14" s="6">
         <v>0.33333333333333331</v>
@@ -957,7 +957,7 @@
         <v>42</v>
       </c>
       <c r="B15" s="5">
-        <v>46196</v>
+        <v>46318</v>
       </c>
       <c r="C15" s="6">
         <v>0.33333333333333331</v>
@@ -971,7 +971,7 @@
         <v>43</v>
       </c>
       <c r="B16" s="5">
-        <v>46197</v>
+        <v>46319</v>
       </c>
       <c r="C16" s="6">
         <v>0.33333333333333331</v>
@@ -985,7 +985,7 @@
         <v>44</v>
       </c>
       <c r="B17" s="5">
-        <v>46198</v>
+        <v>46320</v>
       </c>
       <c r="C17" s="6">
         <v>0.33333333333333331</v>
@@ -999,7 +999,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="5">
-        <v>46199</v>
+        <v>46321</v>
       </c>
       <c r="C18" s="6">
         <v>0.33333333333333331</v>
@@ -1013,7 +1013,7 @@
         <v>33</v>
       </c>
       <c r="B19" s="5">
-        <v>46200</v>
+        <v>46322</v>
       </c>
       <c r="C19" s="6">
         <v>0.33333333333333331</v>
@@ -1027,7 +1027,7 @@
         <v>32</v>
       </c>
       <c r="B20" s="5">
-        <v>46201</v>
+        <v>46323</v>
       </c>
       <c r="C20" s="6">
         <v>0.33333333333333331</v>
@@ -1041,7 +1041,7 @@
         <v>31</v>
       </c>
       <c r="B21" s="5">
-        <v>46202</v>
+        <v>46324</v>
       </c>
       <c r="C21" s="6">
         <v>0.33333333333333331</v>
@@ -1055,7 +1055,7 @@
         <v>45</v>
       </c>
       <c r="B22" s="5">
-        <v>46190</v>
+        <v>46312</v>
       </c>
       <c r="C22" s="6">
         <v>0.58333333333333337</v>
@@ -1069,7 +1069,7 @@
         <v>46</v>
       </c>
       <c r="B23" s="5">
-        <v>46197</v>
+        <v>46319</v>
       </c>
       <c r="C23" s="6">
         <v>0.58333333333333337</v>
@@ -1083,7 +1083,7 @@
         <v>8</v>
       </c>
       <c r="B24" s="5">
-        <v>46193</v>
+        <v>46315</v>
       </c>
       <c r="C24" s="6">
         <v>0.58333333333333337</v>
